--- a/docs/plantillas-de-valorizacion/Módulo 7_ Plantilla Valoración IDC v2024.3_ TIKR.xlsx
+++ b/docs/plantillas-de-valorizacion/Módulo 7_ Plantilla Valoración IDC v2024.3_ TIKR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17E8543-D5EC-47F1-8B7C-324372CD0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3277685-E52D-9742-8FDE-5BA2C2E7E87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="636" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="680" windowWidth="30160" windowHeight="18900" tabRatio="636" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="13" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="8.TIKR_BS" sheetId="10" r:id="rId9"/>
     <sheet name="9.TIKR_CF" sheetId="11" r:id="rId10"/>
     <sheet name="10.Glosario" sheetId="6" r:id="rId11"/>
-    <sheet name="TIKR_Cálculos" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="TIKR_Cálculos" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -204,24 +204,60 @@
           <rPr>
             <b/>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>IDC:</t>
         </r>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve"> 
-Total Interest Expense = Interest Expense + Interest Income
-Número Negativo = gasto // Positivo = ingreso</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Total Interest Expense = Interest Expense + Interest Income
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Número Negativo = gasto // Positivo = ingreso</t>
         </r>
       </text>
     </comment>
@@ -231,7 +267,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -244,12 +280,31 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Introducir en negativo si es un ingreso (devolución de impuestos)
-Taxes Paid = Tax Expense = Impuesto sobre beneficio</t>
+          <t xml:space="preserve">Introducir en negativo si es un ingreso (devolución de impuestos)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Taxes Paid = Tax Expense = Impuesto sobre beneficio</t>
         </r>
       </text>
     </comment>
@@ -831,9 +886,47 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Short-Term Debt, Financial Debt, Borrowings, Loans, Current portion of long-term debt, préstamos a corto plazo, deuda financiera corriente
-Debemos incluir solo la deuda financiera como préstamos, bonos o instrumentos similares (obligaciones, notas), ya que a nivel legal
-Solo incluímos la deuda que conlleve el pago de intereses y pueda hacer quebrar la empresa</t>
+          <t xml:space="preserve">Short-Term Debt, Financial Debt, Borrowings, Loans, Current portion of long-term debt, préstamos a corto plazo, deuda financiera corriente
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Debemos incluir solo la deuda financiera como préstamos, bonos o instrumentos similares (obligaciones, notas), ya que a nivel legal
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Solo incluímos la deuda que conlleve el pago de intereses y pueda hacer quebrar la empresa</t>
         </r>
       </text>
     </comment>
@@ -2509,7 +2602,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2655,6 +2748,19 @@
       <sz val="12"/>
       <color theme="9" tint="-0.24994659260841701"/>
       <name val="Ebrima"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -5082,7 +5188,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5511,6 +5617,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5518,7 +5625,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:blipFill dpi="0" rotWithShape="1">
@@ -5555,7 +5661,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6056,7 +6162,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6591,7 +6697,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7111,6 +7217,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7118,7 +7225,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:blipFill dpi="0" rotWithShape="1">
@@ -7155,7 +7261,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7797,7 +7903,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12335,13 +12441,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>436215</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>21239</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>36180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>1963137</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>304159</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13303,118 +13409,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11C7CDC-1735-4D2B-9DFA-DC9FA9A30865}">
   <dimension ref="A1:O29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="246.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="246.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" hidden="1"/>
+    <col min="16" max="16384" width="11.5" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="87" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:2" ht="87" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:2" ht="22" x14ac:dyDescent="0.2">
       <c r="B2" s="178" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="20"/>
     </row>
-    <row r="4" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="100" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="100"/>
     </row>
-    <row r="6" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="100" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="100"/>
     </row>
-    <row r="8" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="100" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="100"/>
     </row>
-    <row r="10" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="101" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="101"/>
     </row>
-    <row r="12" spans="2:2" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="236" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="101"/>
     </row>
-    <row r="14" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="101" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="53" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:2" ht="22" x14ac:dyDescent="0.2">
       <c r="B16" s="178" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="53"/>
     </row>
-    <row r="18" spans="2:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.2">
       <c r="B18" s="242" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="242"/>
     </row>
-    <row r="20" spans="2:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.2">
       <c r="B20" s="242" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="242"/>
     </row>
-    <row r="22" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="100" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="53"/>
     </row>
-    <row r="24" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="100" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="53"/>
     </row>
-    <row r="26" spans="2:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:2" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13425,15 +13531,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E895F573-FD70-43AA-9C68-646EEB9D54E7}">
   <dimension ref="A1:L99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="3" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" hidden="1"/>
+    <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="79"/>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -13447,7 +13553,7 @@
       <c r="K1" s="80"/>
       <c r="L1" s="80"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="79"/>
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
@@ -13461,7 +13567,7 @@
       <c r="K2" s="81"/>
       <c r="L2" s="81"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="82"/>
       <c r="B3" s="83"/>
       <c r="C3" s="83"/>
@@ -13475,7 +13581,7 @@
       <c r="K3" s="83"/>
       <c r="L3" s="83"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="82"/>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
@@ -13489,7 +13595,7 @@
       <c r="K4" s="84"/>
       <c r="L4" s="84"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="82"/>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -13503,7 +13609,7 @@
       <c r="K5" s="84"/>
       <c r="L5" s="84"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="82"/>
       <c r="B6" s="84"/>
       <c r="C6" s="84"/>
@@ -13517,7 +13623,7 @@
       <c r="K6" s="84"/>
       <c r="L6" s="84"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="82"/>
       <c r="B7" s="84"/>
       <c r="C7" s="84"/>
@@ -13531,7 +13637,7 @@
       <c r="K7" s="84"/>
       <c r="L7" s="84"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="82"/>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
@@ -13545,7 +13651,7 @@
       <c r="K8" s="84"/>
       <c r="L8" s="84"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="82"/>
       <c r="B9" s="84"/>
       <c r="C9" s="84"/>
@@ -13559,7 +13665,7 @@
       <c r="K9" s="84"/>
       <c r="L9" s="84"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="82"/>
       <c r="B10" s="84"/>
       <c r="C10" s="84"/>
@@ -13573,7 +13679,7 @@
       <c r="K10" s="84"/>
       <c r="L10" s="84"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="82"/>
       <c r="B11" s="84"/>
       <c r="C11" s="84"/>
@@ -13587,7 +13693,7 @@
       <c r="K11" s="84"/>
       <c r="L11" s="84"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="82"/>
       <c r="B12" s="84"/>
       <c r="C12" s="84"/>
@@ -13601,7 +13707,7 @@
       <c r="K12" s="84"/>
       <c r="L12" s="84"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="82"/>
       <c r="B13" s="83"/>
       <c r="C13" s="84"/>
@@ -13615,7 +13721,7 @@
       <c r="K13" s="84"/>
       <c r="L13" s="84"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="82"/>
       <c r="B14" s="83"/>
       <c r="C14" s="84"/>
@@ -13629,7 +13735,7 @@
       <c r="K14" s="84"/>
       <c r="L14" s="84"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="82"/>
       <c r="B15" s="84"/>
       <c r="C15" s="84"/>
@@ -13643,7 +13749,7 @@
       <c r="K15" s="84"/>
       <c r="L15" s="84"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="82"/>
       <c r="B16" s="84"/>
       <c r="C16" s="84"/>
@@ -13657,7 +13763,7 @@
       <c r="K16" s="84"/>
       <c r="L16" s="84"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="82"/>
       <c r="B17" s="84"/>
       <c r="C17" s="84"/>
@@ -13671,7 +13777,7 @@
       <c r="K17" s="84"/>
       <c r="L17" s="84"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="82"/>
       <c r="B18" s="84"/>
       <c r="C18" s="84"/>
@@ -13685,7 +13791,7 @@
       <c r="K18" s="84"/>
       <c r="L18" s="84"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="82"/>
       <c r="B19" s="84"/>
       <c r="C19" s="84"/>
@@ -13699,7 +13805,7 @@
       <c r="K19" s="84"/>
       <c r="L19" s="84"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="82"/>
       <c r="B20" s="84"/>
       <c r="C20" s="84"/>
@@ -13713,7 +13819,7 @@
       <c r="K20" s="84"/>
       <c r="L20" s="84"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="82"/>
       <c r="B21" s="84"/>
       <c r="C21" s="84"/>
@@ -13727,7 +13833,7 @@
       <c r="K21" s="84"/>
       <c r="L21" s="84"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="82"/>
       <c r="B22" s="84"/>
       <c r="C22" s="84"/>
@@ -13741,7 +13847,7 @@
       <c r="K22" s="84"/>
       <c r="L22" s="84"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="82"/>
       <c r="B23" s="84"/>
       <c r="C23" s="84"/>
@@ -13755,7 +13861,7 @@
       <c r="K23" s="84"/>
       <c r="L23" s="84"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="82"/>
       <c r="B24" s="84"/>
       <c r="C24" s="84"/>
@@ -13769,7 +13875,7 @@
       <c r="K24" s="84"/>
       <c r="L24" s="84"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="82"/>
       <c r="B25" s="84"/>
       <c r="C25" s="84"/>
@@ -13783,7 +13889,7 @@
       <c r="K25" s="84"/>
       <c r="L25" s="84"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="82"/>
       <c r="B26" s="84"/>
       <c r="C26" s="84"/>
@@ -13797,7 +13903,7 @@
       <c r="K26" s="84"/>
       <c r="L26" s="84"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="82"/>
       <c r="B27" s="84"/>
       <c r="C27" s="84"/>
@@ -13811,7 +13917,7 @@
       <c r="K27" s="84"/>
       <c r="L27" s="84"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="82"/>
       <c r="B28" s="84"/>
       <c r="C28" s="84"/>
@@ -13825,7 +13931,7 @@
       <c r="K28" s="84"/>
       <c r="L28" s="84"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="82"/>
       <c r="B29" s="84"/>
       <c r="C29" s="84"/>
@@ -13839,7 +13945,7 @@
       <c r="K29" s="84"/>
       <c r="L29" s="84"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="82"/>
       <c r="B30" s="84"/>
       <c r="C30" s="84"/>
@@ -13853,7 +13959,7 @@
       <c r="K30" s="84"/>
       <c r="L30" s="84"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="82"/>
       <c r="B31" s="84"/>
       <c r="C31" s="84"/>
@@ -13867,7 +13973,7 @@
       <c r="K31" s="84"/>
       <c r="L31" s="84"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="82"/>
       <c r="B32" s="84"/>
       <c r="C32" s="84"/>
@@ -13881,7 +13987,7 @@
       <c r="K32" s="84"/>
       <c r="L32" s="84"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="82"/>
       <c r="B33" s="84"/>
       <c r="C33" s="84"/>
@@ -13895,7 +14001,7 @@
       <c r="K33" s="84"/>
       <c r="L33" s="84"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="82"/>
       <c r="B34" s="84"/>
       <c r="C34" s="84"/>
@@ -13909,7 +14015,7 @@
       <c r="K34" s="84"/>
       <c r="L34" s="84"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="82"/>
       <c r="B35" s="84"/>
       <c r="C35" s="84"/>
@@ -13923,7 +14029,7 @@
       <c r="K35" s="84"/>
       <c r="L35" s="84"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="82"/>
       <c r="B36" s="84"/>
       <c r="C36" s="84"/>
@@ -13937,7 +14043,7 @@
       <c r="K36" s="84"/>
       <c r="L36" s="84"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="82"/>
       <c r="B37" s="84"/>
       <c r="C37" s="84"/>
@@ -13951,7 +14057,7 @@
       <c r="K37" s="84"/>
       <c r="L37" s="84"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="82"/>
       <c r="B38" s="84"/>
       <c r="C38" s="84"/>
@@ -13965,7 +14071,7 @@
       <c r="K38" s="84"/>
       <c r="L38" s="84"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="82"/>
       <c r="B39" s="84"/>
       <c r="C39" s="84"/>
@@ -13979,7 +14085,7 @@
       <c r="K39" s="84"/>
       <c r="L39" s="84"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="82"/>
       <c r="B40" s="84"/>
       <c r="C40" s="84"/>
@@ -13993,7 +14099,7 @@
       <c r="K40" s="84"/>
       <c r="L40" s="84"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="82"/>
       <c r="B41" s="84"/>
       <c r="C41" s="84"/>
@@ -14007,7 +14113,7 @@
       <c r="K41" s="84"/>
       <c r="L41" s="84"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="82"/>
       <c r="B42" s="84"/>
       <c r="C42" s="84"/>
@@ -14021,7 +14127,7 @@
       <c r="K42" s="84"/>
       <c r="L42" s="84"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="82"/>
       <c r="B43" s="84"/>
       <c r="C43" s="84"/>
@@ -14035,7 +14141,7 @@
       <c r="K43" s="84"/>
       <c r="L43" s="84"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="82"/>
       <c r="B44" s="84"/>
       <c r="C44" s="84"/>
@@ -14049,7 +14155,7 @@
       <c r="K44" s="84"/>
       <c r="L44" s="84"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="82"/>
       <c r="B45" s="84"/>
       <c r="C45" s="84"/>
@@ -14063,7 +14169,7 @@
       <c r="K45" s="84"/>
       <c r="L45" s="84"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="82"/>
       <c r="B46" s="84"/>
       <c r="C46" s="84"/>
@@ -14077,7 +14183,7 @@
       <c r="K46" s="84"/>
       <c r="L46" s="84"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="82"/>
       <c r="B47" s="84"/>
       <c r="C47" s="84"/>
@@ -14091,7 +14197,7 @@
       <c r="K47" s="84"/>
       <c r="L47" s="84"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="82"/>
       <c r="B48" s="83"/>
       <c r="C48" s="83"/>
@@ -14105,7 +14211,7 @@
       <c r="K48" s="84"/>
       <c r="L48" s="84"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="82"/>
       <c r="B49" s="84"/>
       <c r="C49" s="84"/>
@@ -14119,7 +14225,7 @@
       <c r="K49" s="84"/>
       <c r="L49" s="84"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="82"/>
       <c r="B50" s="84"/>
       <c r="C50" s="84"/>
@@ -14133,7 +14239,7 @@
       <c r="K50" s="84"/>
       <c r="L50" s="84"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="82"/>
       <c r="B51" s="84"/>
       <c r="C51" s="84"/>
@@ -14147,7 +14253,7 @@
       <c r="K51" s="84"/>
       <c r="L51" s="84"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="82"/>
       <c r="B52" s="83"/>
       <c r="C52" s="83"/>
@@ -14161,7 +14267,7 @@
       <c r="K52" s="83"/>
       <c r="L52" s="83"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="82"/>
       <c r="B53" s="84"/>
       <c r="C53" s="84"/>
@@ -14175,7 +14281,7 @@
       <c r="K53" s="84"/>
       <c r="L53" s="84"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="82"/>
       <c r="B54" s="84"/>
       <c r="C54" s="84"/>
@@ -14189,7 +14295,7 @@
       <c r="K54" s="84"/>
       <c r="L54" s="84"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="82"/>
       <c r="B55" s="84"/>
       <c r="C55" s="84"/>
@@ -14203,7 +14309,7 @@
       <c r="K55" s="84"/>
       <c r="L55" s="84"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="82"/>
       <c r="B56" s="84"/>
       <c r="C56" s="84"/>
@@ -14217,7 +14323,7 @@
       <c r="K56" s="84"/>
       <c r="L56" s="84"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="82"/>
       <c r="B57" s="84"/>
       <c r="C57" s="84"/>
@@ -14231,7 +14337,7 @@
       <c r="K57" s="84"/>
       <c r="L57" s="84"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="82"/>
       <c r="B58" s="84"/>
       <c r="C58" s="84"/>
@@ -14245,7 +14351,7 @@
       <c r="K58" s="84"/>
       <c r="L58" s="84"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="82"/>
       <c r="B59" s="84"/>
       <c r="C59" s="84"/>
@@ -14259,7 +14365,7 @@
       <c r="K59" s="84"/>
       <c r="L59" s="84"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="82"/>
       <c r="B60" s="84"/>
       <c r="C60" s="84"/>
@@ -14273,7 +14379,7 @@
       <c r="K60" s="84"/>
       <c r="L60" s="84"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="82"/>
       <c r="B61" s="83"/>
       <c r="C61" s="83"/>
@@ -14287,7 +14393,7 @@
       <c r="K61" s="83"/>
       <c r="L61" s="83"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="82"/>
       <c r="B62" s="84"/>
       <c r="C62" s="84"/>
@@ -14301,7 +14407,7 @@
       <c r="K62" s="84"/>
       <c r="L62" s="84"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="82"/>
       <c r="B63" s="84"/>
       <c r="C63" s="84"/>
@@ -14315,7 +14421,7 @@
       <c r="K63" s="84"/>
       <c r="L63" s="84"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="82"/>
       <c r="B64" s="83"/>
       <c r="C64" s="83"/>
@@ -14329,7 +14435,7 @@
       <c r="K64" s="84"/>
       <c r="L64" s="84"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="82"/>
       <c r="B65" s="84"/>
       <c r="C65" s="84"/>
@@ -14343,7 +14449,7 @@
       <c r="K65" s="84"/>
       <c r="L65" s="84"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="82"/>
       <c r="B66" s="83"/>
       <c r="C66" s="83"/>
@@ -14357,7 +14463,7 @@
       <c r="K66" s="83"/>
       <c r="L66" s="83"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="82"/>
       <c r="B67" s="83"/>
       <c r="C67" s="83"/>
@@ -14371,7 +14477,7 @@
       <c r="K67" s="83"/>
       <c r="L67" s="83"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="82"/>
       <c r="B68" s="83"/>
       <c r="C68" s="83"/>
@@ -14385,7 +14491,7 @@
       <c r="K68" s="84"/>
       <c r="L68" s="84"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="82"/>
       <c r="B69" s="83"/>
       <c r="C69" s="83"/>
@@ -14399,7 +14505,7 @@
       <c r="K69" s="84"/>
       <c r="L69" s="84"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="82"/>
       <c r="B70" s="84"/>
       <c r="C70" s="84"/>
@@ -14413,7 +14519,7 @@
       <c r="K70" s="84"/>
       <c r="L70" s="84"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="82"/>
       <c r="B71" s="83"/>
       <c r="C71" s="83"/>
@@ -14427,7 +14533,7 @@
       <c r="K71" s="83"/>
       <c r="L71" s="83"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="82"/>
       <c r="B72" s="83"/>
       <c r="C72" s="83"/>
@@ -14441,7 +14547,7 @@
       <c r="K72" s="83"/>
       <c r="L72" s="83"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="82"/>
       <c r="B73" s="83"/>
       <c r="C73" s="83"/>
@@ -14455,7 +14561,7 @@
       <c r="K73" s="83"/>
       <c r="L73" s="83"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="82"/>
       <c r="B74" s="83"/>
       <c r="C74" s="83"/>
@@ -14469,7 +14575,7 @@
       <c r="K74" s="83"/>
       <c r="L74" s="83"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="82"/>
       <c r="B75" s="83"/>
       <c r="C75" s="83"/>
@@ -14483,7 +14589,7 @@
       <c r="K75" s="83"/>
       <c r="L75" s="83"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="82"/>
       <c r="B76" s="83"/>
       <c r="C76" s="83"/>
@@ -14497,7 +14603,7 @@
       <c r="K76" s="83"/>
       <c r="L76" s="83"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="82"/>
       <c r="B77" s="83"/>
       <c r="C77" s="83"/>
@@ -14511,7 +14617,7 @@
       <c r="K77" s="83"/>
       <c r="L77" s="83"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="82"/>
       <c r="B78" s="83"/>
       <c r="C78" s="83"/>
@@ -14525,7 +14631,7 @@
       <c r="K78" s="83"/>
       <c r="L78" s="83"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="82"/>
       <c r="B79" s="83"/>
       <c r="C79" s="83"/>
@@ -14539,7 +14645,7 @@
       <c r="K79" s="83"/>
       <c r="L79" s="83"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="82"/>
       <c r="B80" s="83"/>
       <c r="C80" s="83"/>
@@ -14553,7 +14659,7 @@
       <c r="K80" s="83"/>
       <c r="L80" s="83"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="82"/>
       <c r="B81" s="83"/>
       <c r="C81" s="83"/>
@@ -14567,7 +14673,7 @@
       <c r="K81" s="83"/>
       <c r="L81" s="83"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="82"/>
       <c r="B82" s="83"/>
       <c r="C82" s="83"/>
@@ -14581,7 +14687,7 @@
       <c r="K82" s="83"/>
       <c r="L82" s="83"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="82"/>
       <c r="B83" s="83"/>
       <c r="C83" s="83"/>
@@ -14595,7 +14701,7 @@
       <c r="K83" s="83"/>
       <c r="L83" s="83"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="82"/>
       <c r="B84" s="83"/>
       <c r="C84" s="83"/>
@@ -14609,7 +14715,7 @@
       <c r="K84" s="83"/>
       <c r="L84" s="83"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="82"/>
       <c r="B85" s="83"/>
       <c r="C85" s="83"/>
@@ -14623,7 +14729,7 @@
       <c r="K85" s="83"/>
       <c r="L85" s="83"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="82"/>
       <c r="B86" s="83"/>
       <c r="C86" s="83"/>
@@ -14637,7 +14743,7 @@
       <c r="K86" s="83"/>
       <c r="L86" s="83"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="82"/>
       <c r="B87" s="83"/>
       <c r="C87" s="83"/>
@@ -14651,7 +14757,7 @@
       <c r="K87" s="83"/>
       <c r="L87" s="83"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="82"/>
       <c r="B88" s="83"/>
       <c r="C88" s="83"/>
@@ -14665,7 +14771,7 @@
       <c r="K88" s="83"/>
       <c r="L88" s="83"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="82"/>
       <c r="B89" s="83"/>
       <c r="C89" s="83"/>
@@ -14679,7 +14785,7 @@
       <c r="K89" s="83"/>
       <c r="L89" s="83"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="82"/>
       <c r="B90" s="83"/>
       <c r="C90" s="83"/>
@@ -14693,7 +14799,7 @@
       <c r="K90" s="83"/>
       <c r="L90" s="83"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="82"/>
       <c r="B91" s="83"/>
       <c r="C91" s="83"/>
@@ -14707,7 +14813,7 @@
       <c r="K91" s="83"/>
       <c r="L91" s="83"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="82"/>
       <c r="B92" s="83"/>
       <c r="C92" s="83"/>
@@ -14721,7 +14827,7 @@
       <c r="K92" s="83"/>
       <c r="L92" s="83"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="82"/>
       <c r="B93" s="83"/>
       <c r="C93" s="83"/>
@@ -14735,7 +14841,7 @@
       <c r="K93" s="83"/>
       <c r="L93" s="83"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="82"/>
       <c r="B94" s="83"/>
       <c r="C94" s="83"/>
@@ -14749,7 +14855,7 @@
       <c r="K94" s="83"/>
       <c r="L94" s="83"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="82"/>
       <c r="B95" s="83"/>
       <c r="C95" s="83"/>
@@ -14763,7 +14869,7 @@
       <c r="K95" s="83"/>
       <c r="L95" s="83"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="82"/>
       <c r="B96" s="83"/>
       <c r="C96" s="83"/>
@@ -14777,7 +14883,7 @@
       <c r="K96" s="83"/>
       <c r="L96" s="83"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="82"/>
       <c r="B97" s="83"/>
       <c r="C97" s="83"/>
@@ -14791,7 +14897,7 @@
       <c r="K97" s="83"/>
       <c r="L97" s="83"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="82"/>
       <c r="B98" s="83"/>
       <c r="C98" s="83"/>
@@ -14805,7 +14911,7 @@
       <c r="K98" s="83"/>
       <c r="L98" s="83"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="82"/>
       <c r="B99" s="83"/>
       <c r="C99" s="83"/>
@@ -14829,23 +14935,23 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2989650-348F-4BAF-A3E8-F193B2547EB0}">
   <dimension ref="A1:T65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="17.25" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.42578125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="6" customWidth="1"/>
     <col min="3" max="3" width="79" style="24" customWidth="1"/>
-    <col min="4" max="4" width="83.42578125" style="24" customWidth="1"/>
-    <col min="5" max="5" width="69.42578125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="56.42578125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="13.85546875" style="6" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="16.85546875" style="6" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="1.85546875" style="6" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="83.5" style="24" customWidth="1"/>
+    <col min="5" max="5" width="69.5" style="24" customWidth="1"/>
+    <col min="6" max="6" width="56.5" style="6" customWidth="1"/>
+    <col min="7" max="8" width="13.83203125" style="6" hidden="1" customWidth="1"/>
+    <col min="9" max="14" width="16.83203125" style="6" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="1.83203125" style="6" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="6" hidden="1" customWidth="1"/>
-    <col min="19" max="21" width="9.140625" style="6" hidden="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="6" hidden="1"/>
+    <col min="19" max="21" width="9.1640625" style="6" hidden="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.1640625" style="6" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
       <c r="B1" s="27"/>
       <c r="C1" s="32"/>
@@ -14865,7 +14971,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="27"/>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27"/>
       <c r="B2" s="38" t="s">
         <v>190</v>
@@ -14895,7 +15001,7 @@
       <c r="S2" s="27"/>
       <c r="T2" s="27"/>
     </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27"/>
       <c r="B3" s="39" t="s">
         <v>2</v>
@@ -14925,7 +15031,7 @@
       <c r="S3" s="27"/>
       <c r="T3" s="27"/>
     </row>
-    <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
       <c r="B4" s="179" t="s">
         <v>4</v>
@@ -14955,7 +15061,7 @@
       <c r="S4" s="27"/>
       <c r="T4" s="27"/>
     </row>
-    <row r="5" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="39" t="s">
         <v>16</v>
@@ -14985,7 +15091,7 @@
       <c r="S5" s="27"/>
       <c r="T5" s="27"/>
     </row>
-    <row r="6" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="27"/>
       <c r="B6" s="179" t="s">
         <v>1</v>
@@ -15013,7 +15119,7 @@
       <c r="S6" s="27"/>
       <c r="T6" s="27"/>
     </row>
-    <row r="7" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
       <c r="B7" s="39" t="s">
         <v>18</v>
@@ -15039,7 +15145,7 @@
       <c r="S7" s="27"/>
       <c r="T7" s="27"/>
     </row>
-    <row r="8" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="27"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -15060,7 +15166,7 @@
       <c r="S8" s="27"/>
       <c r="T8" s="27"/>
     </row>
-    <row r="9" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="27"/>
       <c r="B9" s="37" t="s">
         <v>79</v>
@@ -15090,7 +15196,7 @@
       <c r="S9" s="27"/>
       <c r="T9" s="27"/>
     </row>
-    <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="27"/>
       <c r="B10" s="39" t="s">
         <v>140</v>
@@ -15116,7 +15222,7 @@
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
     </row>
-    <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="27"/>
       <c r="B11" s="179" t="s">
         <v>25</v>
@@ -15142,7 +15248,7 @@
       <c r="S11" s="27"/>
       <c r="T11" s="27"/>
     </row>
-    <row r="12" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="27"/>
       <c r="B12" s="39" t="s">
         <v>23</v>
@@ -15170,7 +15276,7 @@
       <c r="S12" s="27"/>
       <c r="T12" s="27"/>
     </row>
-    <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="27"/>
       <c r="B13" s="179" t="s">
         <v>100</v>
@@ -15196,7 +15302,7 @@
       <c r="S13" s="27"/>
       <c r="T13" s="27"/>
     </row>
-    <row r="14" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="27"/>
       <c r="B14" s="39" t="s">
         <v>101</v>
@@ -15222,7 +15328,7 @@
       <c r="S14" s="27"/>
       <c r="T14" s="27"/>
     </row>
-    <row r="15" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="27"/>
       <c r="B15" s="179" t="s">
         <v>99</v>
@@ -15248,7 +15354,7 @@
       <c r="S15" s="27"/>
       <c r="T15" s="27"/>
     </row>
-    <row r="16" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="27"/>
       <c r="B16" s="39" t="s">
         <v>20</v>
@@ -15276,7 +15382,7 @@
       <c r="S16" s="27"/>
       <c r="T16" s="27"/>
     </row>
-    <row r="17" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="27"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -15297,7 +15403,7 @@
       <c r="S17" s="27"/>
       <c r="T17" s="27"/>
     </row>
-    <row r="18" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="27"/>
       <c r="B18" s="37" t="s">
         <v>80</v>
@@ -15327,7 +15433,7 @@
       <c r="S18" s="27"/>
       <c r="T18" s="27"/>
     </row>
-    <row r="19" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="27"/>
       <c r="B19" s="39" t="s">
         <v>2</v>
@@ -15353,7 +15459,7 @@
       <c r="S19" s="27"/>
       <c r="T19" s="27"/>
     </row>
-    <row r="20" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="27"/>
       <c r="B20" s="179" t="s">
         <v>4</v>
@@ -15379,7 +15485,7 @@
       <c r="S20" s="27"/>
       <c r="T20" s="27"/>
     </row>
-    <row r="21" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="27"/>
       <c r="B21" s="39" t="s">
         <v>39</v>
@@ -15405,7 +15511,7 @@
       <c r="S21" s="27"/>
       <c r="T21" s="27"/>
     </row>
-    <row r="22" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="27"/>
       <c r="B22" s="179" t="s">
         <v>6</v>
@@ -15431,7 +15537,7 @@
       <c r="S22" s="27"/>
       <c r="T22" s="27"/>
     </row>
-    <row r="23" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="27"/>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
@@ -15453,7 +15559,7 @@
       <c r="S23" s="27"/>
       <c r="T23" s="27"/>
     </row>
-    <row r="24" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="27"/>
       <c r="B24" s="37" t="s">
         <v>81</v>
@@ -15483,7 +15589,7 @@
       <c r="S24" s="27"/>
       <c r="T24" s="27"/>
     </row>
-    <row r="25" spans="1:20" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="27"/>
       <c r="B25" s="39" t="s">
         <v>105</v>
@@ -15511,7 +15617,7 @@
       <c r="S25" s="27"/>
       <c r="T25" s="27"/>
     </row>
-    <row r="26" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="27"/>
       <c r="B26" s="179" t="s">
         <v>44</v>
@@ -15537,7 +15643,7 @@
       <c r="S26" s="27"/>
       <c r="T26" s="27"/>
     </row>
-    <row r="27" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="27"/>
       <c r="B27" s="39" t="s">
         <v>45</v>
@@ -15563,7 +15669,7 @@
       <c r="S27" s="27"/>
       <c r="T27" s="27"/>
     </row>
-    <row r="28" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="27"/>
       <c r="B28" s="39"/>
       <c r="C28" s="44"/>
@@ -15585,7 +15691,7 @@
       <c r="S28" s="27"/>
       <c r="T28" s="27"/>
     </row>
-    <row r="29" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="27"/>
       <c r="B29" s="37" t="s">
         <v>6</v>
@@ -15615,7 +15721,7 @@
       <c r="S29" s="27"/>
       <c r="T29" s="27"/>
     </row>
-    <row r="30" spans="1:20" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
       <c r="B30" s="39" t="s">
         <v>50</v>
@@ -15645,7 +15751,7 @@
       <c r="S30" s="27"/>
       <c r="T30" s="27"/>
     </row>
-    <row r="31" spans="1:20" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="35" x14ac:dyDescent="0.2">
       <c r="A31" s="27"/>
       <c r="B31" s="179" t="s">
         <v>55</v>
@@ -15675,7 +15781,7 @@
       <c r="S31" s="27"/>
       <c r="T31" s="27"/>
     </row>
-    <row r="32" spans="1:20" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
       <c r="B32" s="39" t="s">
         <v>51</v>
@@ -15703,7 +15809,7 @@
       <c r="S32" s="27"/>
       <c r="T32" s="27"/>
     </row>
-    <row r="33" spans="1:20" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="27"/>
       <c r="B33" s="179" t="s">
         <v>6</v>
@@ -15729,7 +15835,7 @@
       <c r="S33" s="27"/>
       <c r="T33" s="27"/>
     </row>
-    <row r="34" spans="1:20" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
       <c r="B34" s="47"/>
       <c r="C34" s="48"/>
@@ -15751,7 +15857,7 @@
       <c r="S34" s="27"/>
       <c r="T34" s="27"/>
     </row>
-    <row r="35" spans="1:20" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="27"/>
       <c r="B35" s="47"/>
       <c r="C35" s="48"/>
@@ -15773,7 +15879,7 @@
       <c r="S35" s="27"/>
       <c r="T35" s="27"/>
     </row>
-    <row r="36" spans="1:20" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27"/>
       <c r="B36" s="49"/>
       <c r="C36" s="48"/>
@@ -15795,7 +15901,7 @@
       <c r="S36" s="27"/>
       <c r="T36" s="27"/>
     </row>
-    <row r="37" spans="1:20" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="27"/>
       <c r="B37" s="49"/>
       <c r="C37" s="48"/>
@@ -15817,7 +15923,7 @@
       <c r="S37" s="27"/>
       <c r="T37" s="27"/>
     </row>
-    <row r="38" spans="1:20" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="27"/>
       <c r="B38" s="49"/>
       <c r="C38" s="48"/>
@@ -15839,7 +15945,7 @@
       <c r="S38" s="27"/>
       <c r="T38" s="27"/>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="27"/>
       <c r="B39" s="49"/>
       <c r="C39" s="48"/>
@@ -15861,7 +15967,7 @@
       <c r="S39" s="27"/>
       <c r="T39" s="27"/>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
       <c r="B40" s="49"/>
       <c r="C40" s="48"/>
@@ -15883,7 +15989,7 @@
       <c r="S40" s="27"/>
       <c r="T40" s="27"/>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="27"/>
       <c r="B41" s="49"/>
       <c r="C41" s="48"/>
@@ -15905,7 +16011,7 @@
       <c r="S41" s="27"/>
       <c r="T41" s="27"/>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
       <c r="B42" s="49"/>
       <c r="C42" s="48"/>
@@ -15927,7 +16033,7 @@
       <c r="S42" s="27"/>
       <c r="T42" s="27"/>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="27"/>
       <c r="B43" s="49"/>
       <c r="C43" s="48"/>
@@ -15949,7 +16055,7 @@
       <c r="S43" s="27"/>
       <c r="T43" s="27"/>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
       <c r="B44" s="49"/>
       <c r="C44" s="48"/>
@@ -15971,7 +16077,7 @@
       <c r="S44" s="27"/>
       <c r="T44" s="27"/>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="27"/>
       <c r="B45" s="49"/>
       <c r="C45" s="48"/>
@@ -15993,7 +16099,7 @@
       <c r="S45" s="27"/>
       <c r="T45" s="27"/>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
       <c r="B46" s="49"/>
       <c r="C46" s="48"/>
@@ -16015,7 +16121,7 @@
       <c r="S46" s="27"/>
       <c r="T46" s="27"/>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27"/>
       <c r="B47" s="49"/>
       <c r="C47" s="48"/>
@@ -16037,7 +16143,7 @@
       <c r="S47" s="27"/>
       <c r="T47" s="27"/>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
       <c r="B48" s="49"/>
       <c r="C48" s="48"/>
@@ -16059,7 +16165,7 @@
       <c r="S48" s="27"/>
       <c r="T48" s="27"/>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="27"/>
       <c r="B49" s="49"/>
       <c r="C49" s="48"/>
@@ -16081,7 +16187,7 @@
       <c r="S49" s="27"/>
       <c r="T49" s="27"/>
     </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
       <c r="B50" s="49"/>
       <c r="C50" s="48"/>
@@ -16103,7 +16209,7 @@
       <c r="S50" s="27"/>
       <c r="T50" s="27"/>
     </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27"/>
       <c r="B51" s="49"/>
       <c r="C51" s="48"/>
@@ -16125,7 +16231,7 @@
       <c r="S51" s="27"/>
       <c r="T51" s="27"/>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="27"/>
       <c r="B52" s="49"/>
       <c r="C52" s="48"/>
@@ -16147,7 +16253,7 @@
       <c r="S52" s="27"/>
       <c r="T52" s="27"/>
     </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27"/>
       <c r="B53" s="49"/>
       <c r="C53" s="48"/>
@@ -16169,7 +16275,7 @@
       <c r="S53" s="27"/>
       <c r="T53" s="27"/>
     </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="27"/>
       <c r="B54" s="49"/>
       <c r="C54" s="48"/>
@@ -16191,68 +16297,68 @@
       <c r="S54" s="27"/>
       <c r="T54" s="27"/>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B55" s="50"/>
       <c r="C55" s="51"/>
       <c r="D55" s="51"/>
       <c r="E55" s="51"/>
       <c r="I55" s="27"/>
     </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B56" s="50"/>
       <c r="C56" s="51"/>
       <c r="D56" s="51"/>
       <c r="E56" s="51"/>
     </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B57" s="50"/>
       <c r="C57" s="51"/>
       <c r="D57" s="51"/>
       <c r="E57" s="51"/>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B58" s="50"/>
       <c r="C58" s="51"/>
       <c r="D58" s="51"/>
       <c r="E58" s="51"/>
     </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B59" s="50"/>
       <c r="C59" s="51"/>
       <c r="D59" s="51"/>
       <c r="E59" s="51"/>
     </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B60" s="50"/>
       <c r="C60" s="51"/>
       <c r="D60" s="51"/>
       <c r="E60" s="51"/>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B61" s="50"/>
       <c r="C61" s="51"/>
       <c r="D61" s="51"/>
       <c r="E61" s="51"/>
     </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B62" s="50"/>
       <c r="C62" s="51"/>
       <c r="D62" s="51"/>
       <c r="E62" s="51"/>
     </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B63" s="50"/>
       <c r="C63" s="51"/>
       <c r="D63" s="51"/>
       <c r="E63" s="51"/>
     </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="B64" s="50"/>
       <c r="C64" s="51"/>
       <c r="D64" s="51"/>
       <c r="E64" s="51"/>
     </row>
-    <row r="65" x14ac:dyDescent="0.25"/>
+    <row r="65" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="F27:H27"/>
@@ -16270,13 +16376,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A841EDC-2E42-4F91-A115-07FD192CF777}">
   <dimension ref="A1:N76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="11.42578125" style="216"/>
+    <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="11.5" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="78" t="s">
         <v>112</v>
       </c>
@@ -16321,7 +16427,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -16366,7 +16472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>155</v>
       </c>
@@ -16411,7 +16517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="171" t="s">
         <v>115</v>
       </c>
@@ -16456,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -16501,7 +16607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="171" t="s">
         <v>113</v>
       </c>
@@ -16546,7 +16652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="75" t="s">
         <v>111</v>
       </c>
@@ -16591,7 +16697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="78" t="s">
         <v>118</v>
       </c>
@@ -16636,7 +16742,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>119</v>
       </c>
@@ -16681,7 +16787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="171" t="s">
         <v>137</v>
       </c>
@@ -16726,7 +16832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="75" t="s">
         <v>120</v>
       </c>
@@ -16771,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="78" t="s">
         <v>79</v>
       </c>
@@ -16801,7 +16907,7 @@
       <c r="J14" s="222"/>
       <c r="K14" s="222"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
         <v>122</v>
       </c>
@@ -16826,7 +16932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="78" t="s">
         <v>129</v>
       </c>
@@ -16835,7 +16941,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>131</v>
       </c>
@@ -16844,7 +16950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -16853,7 +16959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>146</v>
       </c>
@@ -16862,7 +16968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -16871,7 +16977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>145</v>
       </c>
@@ -16880,7 +16986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -16889,7 +16995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -16898,7 +17004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>148</v>
       </c>
@@ -16907,7 +17013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -16916,7 +17022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>151</v>
       </c>
@@ -16925,10 +17031,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B28" s="226"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="78" t="s">
         <v>186</v>
       </c>
@@ -16957,7 +17063,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>129</v>
       </c>
@@ -16986,7 +17092,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>187</v>
       </c>
@@ -17017,7 +17123,7 @@
       <c r="I31" s="217"/>
       <c r="K31" s="225"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="243" t="s">
         <v>188</v>
       </c>
@@ -17047,7 +17153,7 @@
       </c>
       <c r="K32" s="225"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="243" t="s">
         <v>189</v>
       </c>
@@ -17076,7 +17182,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>183</v>
       </c>
@@ -17106,7 +17212,7 @@
       </c>
       <c r="J34" s="217"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="243" t="s">
         <v>184</v>
       </c>
@@ -17135,7 +17241,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="243" t="s">
         <v>185</v>
       </c>
@@ -17164,7 +17270,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="243"/>
       <c r="B37" s="217"/>
       <c r="C37" s="245"/>
@@ -17173,10 +17279,10 @@
       <c r="F37" s="245"/>
       <c r="G37" s="245"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B38" s="226"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="78" t="s">
         <v>210</v>
       </c>
@@ -17224,7 +17330,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -17273,7 +17379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -17322,7 +17428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -17371,7 +17477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>162</v>
       </c>
@@ -17420,7 +17526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>195</v>
       </c>
@@ -17469,7 +17575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>221</v>
       </c>
@@ -17516,12 +17622,12 @@
       <c r="L45" s="245"/>
       <c r="N45" s="279"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="75" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="78"/>
       <c r="B48" s="215" t="str">
         <f>'1.IS'!C$2</f>
@@ -17562,7 +17668,7 @@
       <c r="K48" s="215"/>
       <c r="L48" s="224"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="172" t="s">
         <v>91</v>
       </c>
@@ -17604,7 +17710,7 @@
       </c>
       <c r="L49" s="227"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="172" t="s">
         <v>18</v>
       </c>
@@ -17646,7 +17752,7 @@
       </c>
       <c r="L50" s="227"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="172" t="s">
         <v>92</v>
       </c>
@@ -17688,7 +17794,7 @@
       </c>
       <c r="L51" s="227"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="228"/>
       <c r="C52" s="228"/>
@@ -17699,7 +17805,7 @@
       <c r="H52" s="228"/>
       <c r="I52" s="228"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="212" t="s">
         <v>207</v>
       </c>
@@ -17712,7 +17818,7 @@
       <c r="H53" s="228"/>
       <c r="I53" s="228"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="78"/>
       <c r="B54" s="224" t="str">
         <f>'1.IS'!B$2</f>
@@ -17756,7 +17862,7 @@
       </c>
       <c r="L54" s="224"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="172" t="s">
         <v>2</v>
       </c>
@@ -17802,7 +17908,7 @@
       </c>
       <c r="L55" s="229"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="172" t="s">
         <v>4</v>
       </c>
@@ -17848,7 +17954,7 @@
       </c>
       <c r="L56" s="229"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="172" t="s">
         <v>6</v>
       </c>
@@ -17894,7 +18000,7 @@
       </c>
       <c r="L57" s="229"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="228"/>
       <c r="C58" s="227"/>
@@ -17905,7 +18011,7 @@
       <c r="H58" s="227"/>
       <c r="L58" s="228"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="212" t="s">
         <v>208</v>
       </c>
@@ -17918,7 +18024,7 @@
       <c r="H59" s="227"/>
       <c r="L59" s="228"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="78"/>
       <c r="B60" s="224" t="str">
         <f>'1.IS'!B$2</f>
@@ -17962,7 +18068,7 @@
       </c>
       <c r="L60" s="224"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="172" t="s">
         <v>6</v>
       </c>
@@ -18008,7 +18114,7 @@
       </c>
       <c r="L61" s="228"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="172" t="s">
         <v>105</v>
       </c>
@@ -18054,7 +18160,7 @@
       </c>
       <c r="L62" s="227"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="228"/>
       <c r="C63" s="228"/>
@@ -18065,7 +18171,7 @@
       <c r="H63" s="228"/>
       <c r="L63" s="228"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
         <v>209</v>
       </c>
@@ -18111,7 +18217,7 @@
       </c>
       <c r="L64" s="224"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="172" t="s">
         <v>97</v>
       </c>
@@ -18157,7 +18263,7 @@
       </c>
       <c r="L65" s="227"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="172" t="s">
         <v>103</v>
       </c>
@@ -18203,7 +18309,7 @@
       </c>
       <c r="L66" s="227"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="172" t="s">
         <v>94</v>
       </c>
@@ -18249,7 +18355,7 @@
       </c>
       <c r="L67" s="227"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="172" t="s">
         <v>95</v>
       </c>
@@ -18295,7 +18401,7 @@
       </c>
       <c r="L68" s="227"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="172" t="s">
         <v>96</v>
       </c>
@@ -18338,7 +18444,7 @@
       </c>
       <c r="L69" s="227"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="78" t="s">
         <v>166</v>
       </c>
@@ -18386,7 +18492,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="172" t="s">
         <v>167</v>
       </c>
@@ -18431,7 +18537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="172" t="s">
         <v>168</v>
       </c>
@@ -18476,7 +18582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="172" t="s">
         <v>174</v>
       </c>
@@ -18525,7 +18631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="172" t="s">
         <v>176</v>
       </c>
@@ -18574,7 +18680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="172" t="s">
         <v>178</v>
       </c>
@@ -18636,20 +18742,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="17.25" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" style="4" customWidth="1"/>
-    <col min="2" max="16" width="12.28515625" style="5" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="28.42578125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="19.140625" style="5" customWidth="1"/>
-    <col min="20" max="20" width="1.28515625" style="6" customWidth="1"/>
-    <col min="21" max="22" width="11.42578125" style="6" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" style="4" customWidth="1"/>
+    <col min="2" max="16" width="12.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="28.5" style="4" customWidth="1"/>
+    <col min="19" max="19" width="19.1640625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="1.33203125" style="6" customWidth="1"/>
+    <col min="21" max="22" width="11.5" style="6" hidden="1" customWidth="1"/>
     <col min="23" max="24" width="0" style="6" hidden="1" customWidth="1"/>
-    <col min="25" max="16384" width="11.42578125" style="6" hidden="1"/>
+    <col min="25" max="16384" width="11.5" style="6" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="2" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1"/>
       <c r="B1" s="17" t="s">
         <v>68</v>
@@ -18676,7 +18782,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="104" t="s">
         <v>66</v>
       </c>
@@ -18750,7 +18856,7 @@
       <c r="U2" s="27"/>
       <c r="V2" s="27"/>
     </row>
-    <row r="3" spans="1:22" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="113" t="s">
         <v>7</v>
       </c>
@@ -18826,7 +18932,7 @@
       <c r="U3" s="27"/>
       <c r="V3" s="27"/>
     </row>
-    <row r="4" spans="1:22" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>11</v>
       </c>
@@ -18899,7 +19005,7 @@
       <c r="U4" s="27"/>
       <c r="V4" s="27"/>
     </row>
-    <row r="5" spans="1:22" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="116" t="s">
         <v>2</v>
       </c>
@@ -18975,7 +19081,7 @@
       <c r="U5" s="27"/>
       <c r="V5" s="27"/>
     </row>
-    <row r="6" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="67" t="s">
         <v>8</v>
       </c>
@@ -19051,7 +19157,7 @@
       <c r="U6" s="27"/>
       <c r="V6" s="27"/>
     </row>
-    <row r="7" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="67" t="s">
         <v>11</v>
       </c>
@@ -19119,7 +19225,7 @@
       <c r="U7" s="27"/>
       <c r="V7" s="27"/>
     </row>
-    <row r="8" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="118" t="s">
         <v>198</v>
       </c>
@@ -19190,7 +19296,7 @@
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
     </row>
-    <row r="9" spans="1:22" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="113" t="s">
         <v>3</v>
       </c>
@@ -19260,7 +19366,7 @@
       <c r="U9" s="27"/>
       <c r="V9" s="27"/>
     </row>
-    <row r="10" spans="1:22" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
         <v>9</v>
       </c>
@@ -19331,7 +19437,7 @@
       <c r="U10" s="27"/>
       <c r="V10" s="27"/>
     </row>
-    <row r="11" spans="1:22" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="67" t="s">
         <v>11</v>
       </c>
@@ -19399,7 +19505,7 @@
       <c r="U11" s="27"/>
       <c r="V11" s="27"/>
     </row>
-    <row r="12" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="270" t="s">
         <v>197</v>
       </c>
@@ -19470,7 +19576,7 @@
       <c r="U12" s="27"/>
       <c r="V12" s="27"/>
     </row>
-    <row r="13" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="270" t="s">
         <v>200</v>
       </c>
@@ -19542,7 +19648,7 @@
       <c r="U13" s="27"/>
       <c r="V13" s="27"/>
     </row>
-    <row r="14" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="67" t="s">
         <v>109</v>
       </c>
@@ -19612,7 +19718,7 @@
       <c r="U14" s="27"/>
       <c r="V14" s="27"/>
     </row>
-    <row r="15" spans="1:22" ht="24.95" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="25" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A15" s="67" t="s">
         <v>16</v>
       </c>
@@ -19682,7 +19788,7 @@
       <c r="U15" s="27"/>
       <c r="V15" s="27"/>
     </row>
-    <row r="16" spans="1:22" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="118" t="s">
         <v>133</v>
       </c>
@@ -19751,7 +19857,7 @@
       <c r="U16" s="27"/>
       <c r="V16" s="27"/>
     </row>
-    <row r="17" spans="1:22" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="s">
         <v>17</v>
       </c>
@@ -19822,7 +19928,7 @@
       <c r="U17" s="27"/>
       <c r="V17" s="27"/>
     </row>
-    <row r="18" spans="1:22" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A18" s="67" t="s">
         <v>0</v>
       </c>
@@ -19893,7 +19999,7 @@
       <c r="U18" s="27"/>
       <c r="V18" s="27"/>
     </row>
-    <row r="19" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="118" t="s">
         <v>201</v>
       </c>
@@ -19964,7 +20070,7 @@
       <c r="U19" s="27"/>
       <c r="V19" s="27"/>
     </row>
-    <row r="20" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="67" t="s">
         <v>1</v>
       </c>
@@ -20035,7 +20141,7 @@
       <c r="U20" s="27"/>
       <c r="V20" s="27"/>
     </row>
-    <row r="21" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="67" t="s">
         <v>202</v>
       </c>
@@ -20106,7 +20212,7 @@
       <c r="U21" s="27"/>
       <c r="V21" s="27"/>
     </row>
-    <row r="22" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="67" t="s">
         <v>11</v>
       </c>
@@ -20174,7 +20280,7 @@
       <c r="U22" s="27"/>
       <c r="V22" s="27"/>
     </row>
-    <row r="23" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="116" t="s">
         <v>18</v>
       </c>
@@ -20245,7 +20351,7 @@
       <c r="U23" s="27"/>
       <c r="V23" s="27"/>
     </row>
-    <row r="24" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="67" t="s">
         <v>11</v>
       </c>
@@ -20313,7 +20419,7 @@
       <c r="U24" s="27"/>
       <c r="V24" s="27"/>
     </row>
-    <row r="25" spans="1:22" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="118" t="s">
         <v>107</v>
       </c>
@@ -20384,7 +20490,7 @@
       <c r="U25" s="27"/>
       <c r="V25" s="27"/>
     </row>
-    <row r="26" spans="1:22" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67" t="s">
         <v>11</v>
       </c>
@@ -20452,71 +20558,71 @@
       <c r="U26" s="27"/>
       <c r="V26" s="27"/>
     </row>
-    <row r="27" spans="1:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T27" s="27"/>
       <c r="U27" s="27"/>
       <c r="V27" s="27"/>
     </row>
-    <row r="28" spans="1:22" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T28" s="27"/>
       <c r="U28" s="27"/>
       <c r="V28" s="27"/>
     </row>
-    <row r="29" spans="1:22" s="25" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" s="25" customFormat="1" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T29" s="52"/>
       <c r="U29" s="52"/>
       <c r="V29" s="52"/>
     </row>
-    <row r="30" spans="1:22" s="25" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" s="25" customFormat="1" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T30" s="52"/>
       <c r="U30" s="52"/>
       <c r="V30" s="52"/>
     </row>
-    <row r="31" spans="1:22" s="25" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" s="25" customFormat="1" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T31" s="52"/>
       <c r="U31" s="52"/>
       <c r="V31" s="52"/>
     </row>
-    <row r="32" spans="1:22" s="25" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" s="25" customFormat="1" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T32" s="52"/>
       <c r="U32" s="52"/>
       <c r="V32" s="52"/>
     </row>
-    <row r="33" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T33" s="27"/>
       <c r="U33" s="27"/>
       <c r="V33" s="27"/>
     </row>
-    <row r="34" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T34" s="27"/>
       <c r="U34" s="27"/>
       <c r="V34" s="27"/>
     </row>
-    <row r="35" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T35" s="27"/>
       <c r="U35" s="27"/>
       <c r="V35" s="27"/>
     </row>
-    <row r="36" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T36" s="27"/>
       <c r="U36" s="27"/>
       <c r="V36" s="27"/>
     </row>
-    <row r="37" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T37" s="27"/>
       <c r="U37" s="27"/>
       <c r="V37" s="27"/>
     </row>
-    <row r="38" spans="20:22" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="20:22" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T38" s="27"/>
       <c r="U38" s="27"/>
       <c r="V38" s="27"/>
     </row>
-    <row r="48" spans="20:22" ht="18" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="20:22" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="53"/>
     </row>
-    <row r="58" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="53"/>
     </row>
   </sheetData>
@@ -20564,19 +20670,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="56.85546875" style="4" customWidth="1"/>
-    <col min="2" max="11" width="12.28515625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="12.28515625" style="5" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="56.83203125" style="4" customWidth="1"/>
+    <col min="2" max="11" width="12.33203125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="12.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" style="5" customWidth="1"/>
     <col min="18" max="18" width="19" style="4" customWidth="1"/>
-    <col min="19" max="20" width="15.42578125" style="4" hidden="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="4" hidden="1"/>
+    <col min="19" max="20" width="15.5" style="4" hidden="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="249" t="str">
         <f>IF('1.IS'!A1&lt;&gt;"",'1.IS'!A1,"")</f>
         <v/>
@@ -20589,7 +20695,7 @@
       </c>
       <c r="P1" s="281"/>
     </row>
-    <row r="2" spans="1:18" s="6" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="104" t="s">
         <v>67</v>
       </c>
@@ -20655,7 +20761,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:18" s="6" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="6" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
@@ -20721,7 +20827,7 @@
       </c>
       <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="118" t="s">
         <v>153</v>
       </c>
@@ -20787,7 +20893,7 @@
       </c>
       <c r="Q4" s="13"/>
     </row>
-    <row r="5" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>121</v>
       </c>
@@ -20853,7 +20959,7 @@
       </c>
       <c r="Q5" s="13"/>
     </row>
-    <row r="6" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>77</v>
       </c>
@@ -20919,7 +21025,7 @@
       </c>
       <c r="Q6" s="13"/>
     </row>
-    <row r="7" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="128" t="s">
         <v>204</v>
       </c>
@@ -20970,7 +21076,7 @@
       <c r="P7" s="127"/>
       <c r="Q7" s="13"/>
     </row>
-    <row r="8" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="128" t="s">
         <v>205</v>
       </c>
@@ -21021,7 +21127,7 @@
       <c r="P8" s="127"/>
       <c r="Q8" s="13"/>
     </row>
-    <row r="9" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="128" t="s">
         <v>203</v>
       </c>
@@ -21072,7 +21178,7 @@
       <c r="P9" s="127"/>
       <c r="Q9" s="13"/>
     </row>
-    <row r="10" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="128" t="s">
         <v>211</v>
       </c>
@@ -21123,7 +21229,7 @@
       <c r="P10" s="127"/>
       <c r="Q10" s="13"/>
     </row>
-    <row r="11" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>125</v>
       </c>
@@ -21192,7 +21298,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>124</v>
       </c>
@@ -21256,7 +21362,7 @@
       <c r="Q12" s="13"/>
       <c r="R12" s="282"/>
     </row>
-    <row r="13" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>108</v>
       </c>
@@ -21323,7 +21429,7 @@
       <c r="Q13" s="13"/>
       <c r="R13" s="282"/>
     </row>
-    <row r="14" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
         <v>13</v>
       </c>
@@ -21389,7 +21495,7 @@
       </c>
       <c r="Q14" s="13"/>
     </row>
-    <row r="15" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="130" t="s">
         <v>93</v>
       </c>
@@ -21455,7 +21561,7 @@
       </c>
       <c r="Q15" s="13"/>
     </row>
-    <row r="16" spans="1:18" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="67" t="s">
         <v>11</v>
       </c>
@@ -21518,7 +21624,7 @@
       </c>
       <c r="Q16" s="13"/>
     </row>
-    <row r="17" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="67" t="s">
         <v>106</v>
       </c>
@@ -21584,7 +21690,7 @@
       </c>
       <c r="Q17" s="14"/>
     </row>
-    <row r="18" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="67" t="s">
         <v>11</v>
       </c>
@@ -21647,7 +21753,7 @@
       </c>
       <c r="Q18" s="14"/>
     </row>
-    <row r="19" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="165" t="s">
         <v>144</v>
       </c>
@@ -21713,7 +21819,7 @@
       </c>
       <c r="Q19" s="14"/>
     </row>
-    <row r="20" spans="1:17" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -21732,7 +21838,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" s="6" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="6" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
         <v>70</v>
       </c>
@@ -21802,7 +21908,7 @@
 -</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>60</v>
       </c>
@@ -21871,7 +21977,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:17" s="6" customFormat="1" ht="24.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" s="6" customFormat="1" ht="24.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>59</v>
       </c>
@@ -21940,7 +22046,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>64</v>
       </c>
@@ -22009,7 +22115,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="23" t="s">
         <v>76</v>
       </c>
@@ -22078,7 +22184,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="67"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -22097,7 +22203,7 @@
       <c r="P26" s="10"/>
       <c r="Q26" s="102"/>
     </row>
-    <row r="27" spans="1:17" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="104" t="s">
         <v>134</v>
       </c>
@@ -22152,7 +22258,7 @@
       <c r="P27" s="10"/>
       <c r="Q27" s="102"/>
     </row>
-    <row r="28" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
         <v>159</v>
       </c>
@@ -22206,7 +22312,7 @@
       <c r="P28" s="10"/>
       <c r="Q28" s="102"/>
     </row>
-    <row r="29" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
         <v>181</v>
       </c>
@@ -22260,7 +22366,7 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="102"/>
     </row>
-    <row r="30" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="18" t="s">
         <v>136</v>
       </c>
@@ -22311,7 +22417,7 @@
       <c r="M30" s="253"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
         <v>135</v>
       </c>
@@ -22362,7 +22468,7 @@
       <c r="M31" s="253"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="174" t="s">
         <v>195</v>
       </c>
@@ -22413,7 +22519,7 @@
       <c r="M32" s="253"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="173" t="s">
         <v>138</v>
       </c>
@@ -22463,7 +22569,7 @@
       </c>
       <c r="M33" s="214"/>
     </row>
-    <row r="35" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="10"/>
@@ -22471,7 +22577,7 @@
       <c r="P35" s="10"/>
       <c r="Q35" s="102"/>
     </row>
-    <row r="36" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="10"/>
@@ -22479,7 +22585,7 @@
       <c r="P36" s="10"/>
       <c r="Q36" s="102"/>
     </row>
-    <row r="37" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="6"/>
@@ -22487,7 +22593,7 @@
       <c r="P37" s="10"/>
       <c r="Q37" s="102"/>
     </row>
-    <row r="38" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="6"/>
@@ -22495,16 +22601,16 @@
       <c r="P38" s="10"/>
       <c r="Q38" s="102"/>
     </row>
-    <row r="39" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L40" s="102"/>
       <c r="M40" s="102"/>
     </row>
-    <row r="41" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="10"/>
@@ -22512,54 +22618,54 @@
       <c r="P41" s="10"/>
       <c r="Q41" s="102"/>
     </row>
-    <row r="42" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L42" s="214"/>
       <c r="M42" s="102"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L43" s="214"/>
       <c r="M43" s="102"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="12:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="12:13" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L63" s="69"/>
       <c r="M63" s="69"/>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L64" s="214"/>
       <c r="M64" s="214"/>
     </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L65" s="214"/>
       <c r="M65" s="214"/>
     </row>
-    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L66" s="214"/>
       <c r="M66" s="214"/>
     </row>
-    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L67" s="214"/>
       <c r="M67" s="214"/>
     </row>
-    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="12:13" ht="17" x14ac:dyDescent="0.2">
       <c r="L68" s="214"/>
       <c r="M68" s="214"/>
     </row>
@@ -22588,19 +22694,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V1048576"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12.28515625" style="5" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="24.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="15.42578125" style="5" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" style="5" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="4" hidden="1"/>
+    <col min="1" max="1" width="51.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12.33203125" style="5" customWidth="1"/>
+    <col min="17" max="18" width="14.6640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5" style="5" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5" style="5" hidden="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.1640625" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="249" t="str">
         <f>IF('1.IS'!A1&lt;&gt;"",'1.IS'!A1,"")</f>
         <v/>
@@ -22614,7 +22720,7 @@
       <c r="P1" s="281"/>
       <c r="V1" s="21"/>
     </row>
-    <row r="2" spans="1:22" s="6" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="104" t="s">
         <v>98</v>
       </c>
@@ -22681,7 +22787,7 @@
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
     </row>
-    <row r="3" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="s">
         <v>14</v>
       </c>
@@ -22749,7 +22855,7 @@
       <c r="R3" s="87"/>
       <c r="V3" s="11"/>
     </row>
-    <row r="4" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105" t="s">
         <v>117</v>
       </c>
@@ -22817,7 +22923,7 @@
       <c r="R4" s="87"/>
       <c r="V4" s="11"/>
     </row>
-    <row r="5" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="105" t="s">
         <v>15</v>
       </c>
@@ -22885,7 +22991,7 @@
       <c r="R5" s="87"/>
       <c r="V5" s="11"/>
     </row>
-    <row r="6" spans="1:22" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="105" t="s">
         <v>61</v>
       </c>
@@ -22953,7 +23059,7 @@
       <c r="R6" s="87"/>
       <c r="V6" s="11"/>
     </row>
-    <row r="7" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="105" t="s">
         <v>62</v>
       </c>
@@ -23024,7 +23130,7 @@
       <c r="U7" s="87"/>
       <c r="V7" s="11"/>
     </row>
-    <row r="8" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="105" t="s">
         <v>126</v>
       </c>
@@ -23095,7 +23201,7 @@
       <c r="U8" s="87"/>
       <c r="V8" s="11"/>
     </row>
-    <row r="9" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="105" t="s">
         <v>127</v>
       </c>
@@ -23166,7 +23272,7 @@
       <c r="U9" s="87"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="105" t="s">
         <v>12</v>
       </c>
@@ -23237,7 +23343,7 @@
       <c r="U10" s="87"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:22" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>104</v>
       </c>
@@ -23308,11 +23414,11 @@
       <c r="U11" s="87"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="V12" s="21"/>
     </row>
-    <row r="13" spans="1:22" s="145" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" s="145" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="58" t="s">
         <v>71</v>
       </c>
@@ -23382,7 +23488,7 @@
  - </v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" s="12" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="185" t="s">
         <v>44</v>
       </c>
@@ -23455,7 +23561,7 @@
       <c r="T14" s="166"/>
       <c r="U14" s="166"/>
     </row>
-    <row r="15" spans="1:22" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" s="12" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
         <v>105</v>
       </c>
@@ -23528,7 +23634,7 @@
       <c r="T15" s="166"/>
       <c r="U15" s="166"/>
     </row>
-    <row r="16" spans="1:22" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" s="12" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="167" t="s">
         <v>128</v>
       </c>
@@ -23596,7 +23702,7 @@
       <c r="T16" s="166"/>
       <c r="U16" s="166"/>
     </row>
-    <row r="17" spans="1:16" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="169"/>
       <c r="C17" s="169"/>
@@ -23609,19 +23715,19 @@
       <c r="J17" s="169"/>
       <c r="K17" s="169"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="K18" s="168"/>
       <c r="L18" s="168"/>
       <c r="P18" s="168"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="L19" s="168"/>
       <c r="M19" s="168"/>
       <c r="N19" s="168"/>
       <c r="O19" s="168"/>
       <c r="P19" s="168"/>
     </row>
-    <row r="1048576" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1048576" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="O1:P1"/>
@@ -23635,16 +23741,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.5703125" style="19" customWidth="1"/>
-    <col min="2" max="16" width="12.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="46.5" style="19" customWidth="1"/>
+    <col min="2" max="16" width="12.33203125" style="3" customWidth="1"/>
     <col min="17" max="17" width="38" customWidth="1"/>
     <col min="18" max="25" width="0" hidden="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" hidden="1"/>
+    <col min="26" max="16384" width="9.1640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="249" t="str">
         <f>IF('1.IS'!A1&lt;&gt;"",'1.IS'!A1,"")</f>
         <v/>
@@ -23657,7 +23763,7 @@
       </c>
       <c r="P1" s="281"/>
     </row>
-    <row r="2" spans="1:17" s="6" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="104" t="s">
         <v>123</v>
       </c>
@@ -23722,7 +23828,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="s">
         <v>10</v>
       </c>
@@ -23760,7 +23866,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
         <v>129</v>
       </c>
@@ -23825,7 +23931,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>116</v>
       </c>
@@ -23893,7 +23999,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A6" s="148" t="s">
         <v>23</v>
       </c>
@@ -23931,7 +24037,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>2</v>
       </c>
@@ -23997,7 +24103,7 @@
       </c>
       <c r="Q7" s="24"/>
     </row>
-    <row r="8" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>4</v>
       </c>
@@ -24063,7 +24169,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
         <v>5</v>
       </c>
@@ -24129,7 +24235,7 @@
       </c>
       <c r="Q9" s="24"/>
     </row>
-    <row r="10" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
         <v>6</v>
       </c>
@@ -24195,7 +24301,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" spans="1:17" s="6" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="6" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24214,7 +24320,7 @@
       <c r="P11" s="91"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="286" t="s">
         <v>19</v>
       </c>
@@ -24228,7 +24334,7 @@
       <c r="P12" s="91"/>
       <c r="Q12" s="24"/>
     </row>
-    <row r="13" spans="1:17" s="6" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="6" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="67"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -24246,7 +24352,7 @@
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
     </row>
-    <row r="14" spans="1:17" s="6" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="6" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="147" t="s">
         <v>89</v>
       </c>
@@ -24271,7 +24377,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A15" s="152" t="s">
         <v>20</v>
       </c>
@@ -24299,7 +24405,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="116" t="s">
         <v>99</v>
       </c>
@@ -24329,7 +24435,7 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="61" t="s">
         <v>100</v>
       </c>
@@ -24357,7 +24463,7 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
         <v>101</v>
       </c>
@@ -24386,7 +24492,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="24"/>
     </row>
-    <row r="19" spans="1:17" s="6" customFormat="1" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="6" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67"/>
       <c r="B19" s="154"/>
       <c r="C19" s="72"/>
@@ -24404,7 +24510,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" spans="1:17" s="6" customFormat="1" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="6" customFormat="1" ht="35" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A20" s="147" t="s">
         <v>74</v>
       </c>
@@ -24443,7 +24549,7 @@
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
     </row>
-    <row r="21" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>63</v>
       </c>
@@ -24479,7 +24585,7 @@
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
     </row>
-    <row r="22" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="155" t="s">
         <v>102</v>
       </c>
@@ -24515,7 +24621,7 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
-    <row r="23" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>100</v>
       </c>
@@ -24551,7 +24657,7 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
-    <row r="24" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="67" t="s">
         <v>101</v>
       </c>
@@ -24587,7 +24693,7 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
     </row>
-    <row r="25" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="175" t="s">
         <v>58</v>
       </c>
@@ -24623,7 +24729,7 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
     </row>
-    <row r="26" spans="1:17" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="6" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="162" t="s">
         <v>215</v>
       </c>
@@ -24658,7 +24764,7 @@
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
     </row>
-    <row r="27" spans="1:17" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
@@ -24669,7 +24775,7 @@
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
     </row>
-    <row r="28" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
@@ -24680,7 +24786,7 @@
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
     </row>
-    <row r="29" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
@@ -24691,7 +24797,7 @@
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
     </row>
-    <row r="30" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
@@ -24702,7 +24808,7 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:17" s="6" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" s="6" customFormat="1" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
@@ -24713,7 +24819,7 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="1:17" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
@@ -24724,7 +24830,7 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
-    <row r="33" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="25"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -24742,7 +24848,7 @@
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
     </row>
-    <row r="34" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="25"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -24760,7 +24866,7 @@
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
     </row>
-    <row r="35" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="25"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -24778,7 +24884,7 @@
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
     </row>
-    <row r="36" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -24794,7 +24900,7 @@
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
-    <row r="37" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -24810,7 +24916,7 @@
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
     </row>
-    <row r="38" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -24826,7 +24932,7 @@
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
-    <row r="39" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -24842,7 +24948,7 @@
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
     </row>
-    <row r="40" spans="1:16" s="6" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" s="6" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -24858,7 +24964,7 @@
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
     </row>
-    <row r="41" spans="1:16" s="4" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" s="4" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="20"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -24876,7 +24982,7 @@
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
     </row>
-    <row r="42" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A42" s="20"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -24894,7 +25000,7 @@
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
     </row>
-    <row r="43" spans="1:16" s="4" customFormat="1" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" s="4" customFormat="1" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="67"/>
       <c r="B43" s="6"/>
       <c r="C43" s="146" t="s">
@@ -24915,7 +25021,7 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
     </row>
-    <row r="44" spans="1:16" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="277" t="s">
         <v>218</v>
       </c>
@@ -24933,7 +25039,7 @@
       <c r="E44" s="285"/>
       <c r="G44" s="159"/>
     </row>
-    <row r="45" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D43:E43"/>
@@ -24977,17 +25083,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9816D559-2DC7-4A02-B3CD-8F2B3A304BDE}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="56.85546875" style="4" customWidth="1"/>
-    <col min="2" max="16" width="14.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="56.83203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="14.6640625" style="5" customWidth="1"/>
     <col min="17" max="17" width="17" style="5" customWidth="1"/>
     <col min="18" max="18" width="19" style="4" customWidth="1"/>
-    <col min="19" max="20" width="15.42578125" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="4"/>
+    <col min="19" max="20" width="15.5" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="str">
         <f>IF('1.IS'!A1&lt;&gt;"",'1.IS'!A1,"")</f>
         <v/>
@@ -24997,7 +25103,7 @@
       </c>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="104" t="s">
         <v>169</v>
       </c>
@@ -25048,7 +25154,7 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="102"/>
     </row>
-    <row r="3" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="239" t="s">
         <v>175</v>
       </c>
@@ -25069,7 +25175,7 @@
       <c r="P3" s="10"/>
       <c r="Q3" s="102"/>
     </row>
-    <row r="4" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="233" t="s">
         <v>163</v>
       </c>
@@ -25120,7 +25226,7 @@
       <c r="P4" s="10"/>
       <c r="Q4" s="102"/>
     </row>
-    <row r="5" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="233" t="s">
         <v>164</v>
       </c>
@@ -25171,7 +25277,7 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="102"/>
     </row>
-    <row r="6" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="233" t="s">
         <v>182</v>
       </c>
@@ -25222,7 +25328,7 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="102"/>
     </row>
-    <row r="7" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="234" t="s">
         <v>165</v>
       </c>
@@ -25270,7 +25376,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="173"/>
       <c r="B8" s="102"/>
       <c r="C8" s="102"/>
@@ -25285,7 +25391,7 @@
       <c r="L8" s="102"/>
       <c r="M8" s="102"/>
     </row>
-    <row r="9" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="104" t="s">
         <v>170</v>
       </c>
@@ -25308,7 +25414,7 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="102"/>
     </row>
-    <row r="10" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="239" t="s">
         <v>171</v>
       </c>
@@ -25326,7 +25432,7 @@
       <c r="M10" s="102"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="233" t="s">
         <v>172</v>
       </c>
@@ -25347,7 +25453,7 @@
       <c r="M11" s="102"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="233" t="s">
         <v>173</v>
       </c>
@@ -25356,7 +25462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="233" t="s">
         <v>174</v>
       </c>
@@ -25365,7 +25471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="233" t="s">
         <v>176</v>
       </c>
@@ -25374,7 +25480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="234" t="s">
         <v>178</v>
       </c>
@@ -25383,8 +25489,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="240"/>
       <c r="C17" s="240"/>
       <c r="D17" s="240"/>
@@ -25396,68 +25502,68 @@
       <c r="J17" s="240"/>
       <c r="K17" s="240"/>
     </row>
-    <row r="18" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
     </row>
-    <row r="21" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
     </row>
-    <row r="27" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
     </row>
-    <row r="28" spans="1:20" s="5" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
     </row>
-    <row r="31" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="L31" s="69"/>
       <c r="M31" s="69"/>
@@ -25465,7 +25571,7 @@
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
     </row>
-    <row r="32" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="L32" s="214"/>
       <c r="M32" s="214"/>
@@ -25473,7 +25579,7 @@
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
     </row>
-    <row r="33" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="L33" s="214"/>
       <c r="M33" s="214"/>
@@ -25481,7 +25587,7 @@
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="L34" s="214"/>
       <c r="M34" s="214"/>
@@ -25489,7 +25595,7 @@
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="L35" s="214"/>
       <c r="M35" s="214"/>
@@ -25497,7 +25603,7 @@
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
     </row>
-    <row r="36" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="L36" s="214"/>
       <c r="M36" s="214"/>
@@ -25531,16 +25637,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB878F2D-A912-4254-99DB-696E457A7EE4}">
   <dimension ref="A1:S86"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.7109375" style="5" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" style="5" customWidth="1"/>
-    <col min="10" max="19" width="11.42578125" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="4" hidden="1"/>
+    <col min="1" max="1" width="41.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.6640625" style="5" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" style="5" customWidth="1"/>
+    <col min="10" max="19" width="11.5" style="4" customWidth="1"/>
+    <col min="20" max="16384" width="11.5" style="4" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="str">
         <f>IF('1.IS'!A1&lt;&gt;"",'1.IS'!A1,"")</f>
         <v/>
@@ -25549,30 +25655,30 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:2" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:2" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="17"/>
     </row>
-    <row r="33" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="164"/>
       <c r="C52" s="164"/>
       <c r="D52" s="164"/>
@@ -25582,7 +25688,7 @@
       <c r="H52" s="164"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="53" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="164"/>
       <c r="C53" s="164"/>
       <c r="D53" s="164"/>
@@ -25592,7 +25698,7 @@
       <c r="H53" s="164"/>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="164"/>
       <c r="C54" s="164"/>
       <c r="D54" s="164"/>
@@ -25602,7 +25708,7 @@
       <c r="H54" s="164"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="164"/>
       <c r="C55" s="164"/>
       <c r="D55" s="164"/>
@@ -25612,7 +25718,7 @@
       <c r="H55" s="164"/>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -25622,7 +25728,7 @@
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -25632,7 +25738,7 @@
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -25642,7 +25748,7 @@
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -25652,7 +25758,7 @@
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -25662,7 +25768,7 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
     </row>
-    <row r="61" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -25672,7 +25778,7 @@
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
     </row>
-    <row r="62" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -25682,7 +25788,7 @@
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -25692,7 +25798,7 @@
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
     </row>
-    <row r="64" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -25702,7 +25808,7 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -25712,7 +25818,7 @@
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
     </row>
-    <row r="66" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -25722,7 +25828,7 @@
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -25732,7 +25838,7 @@
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -25742,7 +25848,7 @@
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -25752,7 +25858,7 @@
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
     </row>
-    <row r="70" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -25762,7 +25868,7 @@
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
     </row>
-    <row r="71" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -25772,7 +25878,7 @@
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -25782,7 +25888,7 @@
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
     </row>
-    <row r="73" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -25792,7 +25898,7 @@
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -25802,7 +25908,7 @@
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -25812,7 +25918,7 @@
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -25822,7 +25928,7 @@
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
     </row>
-    <row r="77" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -25832,7 +25938,7 @@
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
     </row>
-    <row r="78" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -25842,7 +25948,7 @@
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -25852,7 +25958,7 @@
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
     </row>
-    <row r="80" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -25862,7 +25968,7 @@
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
     </row>
-    <row r="81" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -25872,7 +25978,7 @@
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -25882,7 +25988,7 @@
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
     </row>
-    <row r="83" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -25892,7 +25998,7 @@
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
     </row>
-    <row r="84" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -25902,7 +26008,7 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
     </row>
-    <row r="85" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -25912,7 +26018,7 @@
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
     </row>
-    <row r="86" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -25932,15 +26038,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42FADD4-C8A4-4400-B68A-D96FC1366435}">
   <dimension ref="A2:L68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="3" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" hidden="1"/>
+    <col min="1" max="1" width="48.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="75" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" s="75" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="77"/>
       <c r="C2" s="77"/>
       <c r="D2" s="77"/>
@@ -25953,7 +26059,7 @@
       <c r="K2" s="77"/>
       <c r="L2" s="77"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="74"/>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -25966,7 +26072,7 @@
       <c r="K3" s="74"/>
       <c r="L3" s="74"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="74"/>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -25979,7 +26085,7 @@
       <c r="K4" s="74"/>
       <c r="L4" s="74"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="74"/>
       <c r="C5" s="74"/>
       <c r="D5" s="74"/>
@@ -25992,7 +26098,7 @@
       <c r="K5" s="74"/>
       <c r="L5" s="74"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="74"/>
       <c r="C6" s="74"/>
       <c r="D6" s="74"/>
@@ -26005,7 +26111,7 @@
       <c r="K6" s="74"/>
       <c r="L6" s="74"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -26018,7 +26124,7 @@
       <c r="K7" s="74"/>
       <c r="L7" s="74"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="74"/>
       <c r="C8" s="74"/>
       <c r="D8" s="74"/>
@@ -26031,7 +26137,7 @@
       <c r="K8" s="74"/>
       <c r="L8" s="74"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="74"/>
       <c r="C9" s="74"/>
       <c r="D9" s="74"/>
@@ -26044,7 +26150,7 @@
       <c r="K9" s="74"/>
       <c r="L9" s="74"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="74"/>
       <c r="C10" s="74"/>
       <c r="D10" s="74"/>
@@ -26057,7 +26163,7 @@
       <c r="K10" s="74"/>
       <c r="L10" s="74"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="74"/>
       <c r="C11" s="74"/>
       <c r="D11" s="74"/>
@@ -26070,7 +26176,7 @@
       <c r="K11" s="74"/>
       <c r="L11" s="74"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="74"/>
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
@@ -26083,7 +26189,7 @@
       <c r="K12" s="74"/>
       <c r="L12" s="74"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
       <c r="D13" s="74"/>
@@ -26096,7 +26202,7 @@
       <c r="K13" s="74"/>
       <c r="L13" s="74"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -26109,7 +26215,7 @@
       <c r="K14" s="74"/>
       <c r="L14" s="74"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="74"/>
       <c r="C15" s="74"/>
       <c r="D15" s="74"/>
@@ -26122,7 +26228,7 @@
       <c r="K15" s="74"/>
       <c r="L15" s="74"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="74"/>
       <c r="C16" s="74"/>
       <c r="D16" s="74"/>
@@ -26135,7 +26241,7 @@
       <c r="K16" s="74"/>
       <c r="L16" s="74"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="74"/>
       <c r="C17" s="74"/>
       <c r="D17" s="74"/>
@@ -26148,7 +26254,7 @@
       <c r="K17" s="74"/>
       <c r="L17" s="74"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="74"/>
       <c r="C18" s="74"/>
       <c r="D18" s="74"/>
@@ -26161,7 +26267,7 @@
       <c r="K18" s="74"/>
       <c r="L18" s="74"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
       <c r="D19" s="74"/>
@@ -26174,7 +26280,7 @@
       <c r="K19" s="74"/>
       <c r="L19" s="74"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
@@ -26187,7 +26293,7 @@
       <c r="K20" s="74"/>
       <c r="L20" s="74"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
       <c r="D21" s="74"/>
@@ -26200,7 +26306,7 @@
       <c r="K21" s="74"/>
       <c r="L21" s="74"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -26213,7 +26319,7 @@
       <c r="K22" s="74"/>
       <c r="L22" s="74"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -26226,7 +26332,7 @@
       <c r="K23" s="74"/>
       <c r="L23" s="74"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
@@ -26239,7 +26345,7 @@
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
@@ -26252,7 +26358,7 @@
       <c r="K25" s="74"/>
       <c r="L25" s="74"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
@@ -26265,7 +26371,7 @@
       <c r="K26" s="74"/>
       <c r="L26" s="74"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
       <c r="D27" s="74"/>
@@ -26278,7 +26384,7 @@
       <c r="K27" s="74"/>
       <c r="L27" s="74"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="74"/>
       <c r="C28" s="74"/>
       <c r="D28" s="74"/>
@@ -26291,7 +26397,7 @@
       <c r="K28" s="74"/>
       <c r="L28" s="74"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
       <c r="D29" s="74"/>
@@ -26304,7 +26410,7 @@
       <c r="K29" s="74"/>
       <c r="L29" s="74"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
       <c r="D30" s="74"/>
@@ -26317,7 +26423,7 @@
       <c r="K30" s="74"/>
       <c r="L30" s="74"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -26330,7 +26436,7 @@
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
@@ -26343,7 +26449,7 @@
       <c r="K32" s="74"/>
       <c r="L32" s="74"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
@@ -26356,7 +26462,7 @@
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>
@@ -26369,7 +26475,7 @@
       <c r="K34" s="74"/>
       <c r="L34" s="74"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>
@@ -26382,7 +26488,7 @@
       <c r="K35" s="74"/>
       <c r="L35" s="74"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="74"/>
       <c r="C36" s="74"/>
       <c r="D36" s="74"/>
@@ -26395,7 +26501,7 @@
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C37" s="74"/>
       <c r="F37" s="74"/>
       <c r="H37" s="74"/>
@@ -26403,7 +26509,7 @@
       <c r="K37" s="74"/>
       <c r="L37" s="74"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
       <c r="D38" s="74"/>
@@ -26416,7 +26522,7 @@
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
       <c r="D39" s="74"/>
@@ -26429,7 +26535,7 @@
       <c r="K39" s="74"/>
       <c r="L39" s="74"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
       <c r="D40" s="74"/>
@@ -26442,7 +26548,7 @@
       <c r="K40" s="74"/>
       <c r="L40" s="74"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
@@ -26455,7 +26561,7 @@
       <c r="K41" s="74"/>
       <c r="L41" s="74"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
       <c r="D42" s="74"/>
@@ -26468,7 +26574,7 @@
       <c r="K42" s="74"/>
       <c r="L42" s="74"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
@@ -26481,7 +26587,7 @@
       <c r="K43" s="74"/>
       <c r="L43" s="74"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
@@ -26494,7 +26600,7 @@
       <c r="K44" s="74"/>
       <c r="L44" s="74"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
@@ -26507,7 +26613,7 @@
       <c r="K45" s="74"/>
       <c r="L45" s="74"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
@@ -26520,7 +26626,7 @@
       <c r="K46" s="74"/>
       <c r="L46" s="74"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="74"/>
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
@@ -26533,7 +26639,7 @@
       <c r="K47" s="74"/>
       <c r="L47" s="74"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="74"/>
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
@@ -26546,7 +26652,7 @@
       <c r="K48" s="74"/>
       <c r="L48" s="74"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="74"/>
       <c r="C49" s="74"/>
       <c r="D49" s="74"/>
@@ -26559,7 +26665,7 @@
       <c r="K49" s="74"/>
       <c r="L49" s="74"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50" s="74"/>
       <c r="C50" s="74"/>
       <c r="D50" s="74"/>
@@ -26572,7 +26678,7 @@
       <c r="K50" s="74"/>
       <c r="L50" s="74"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" s="74"/>
       <c r="C51" s="74"/>
       <c r="D51" s="74"/>
@@ -26585,7 +26691,7 @@
       <c r="K51" s="74"/>
       <c r="L51" s="74"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" s="74"/>
       <c r="C52" s="74"/>
       <c r="D52" s="74"/>
@@ -26598,7 +26704,7 @@
       <c r="K52" s="74"/>
       <c r="L52" s="74"/>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53" s="74"/>
       <c r="C53" s="74"/>
       <c r="D53" s="74"/>
@@ -26611,7 +26717,7 @@
       <c r="K53" s="74"/>
       <c r="L53" s="74"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54" s="74"/>
       <c r="C54" s="74"/>
       <c r="D54" s="74"/>
@@ -26624,7 +26730,7 @@
       <c r="K54" s="74"/>
       <c r="L54" s="74"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55" s="74"/>
       <c r="C55" s="74"/>
       <c r="D55" s="74"/>
@@ -26637,7 +26743,7 @@
       <c r="K55" s="74"/>
       <c r="L55" s="74"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" s="74"/>
       <c r="C56" s="74"/>
       <c r="D56" s="74"/>
@@ -26650,7 +26756,7 @@
       <c r="K56" s="74"/>
       <c r="L56" s="74"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57" s="74"/>
       <c r="C57" s="74"/>
       <c r="D57" s="74"/>
@@ -26663,7 +26769,7 @@
       <c r="K57" s="74"/>
       <c r="L57" s="74"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="74"/>
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
@@ -26676,7 +26782,7 @@
       <c r="K58" s="74"/>
       <c r="L58" s="74"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="74"/>
       <c r="C59" s="74"/>
       <c r="D59" s="74"/>
@@ -26689,7 +26795,7 @@
       <c r="K59" s="74"/>
       <c r="L59" s="74"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
       <c r="D60" s="74"/>
@@ -26702,7 +26808,7 @@
       <c r="K60" s="74"/>
       <c r="L60" s="74"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
       <c r="D61" s="74"/>
@@ -26715,7 +26821,7 @@
       <c r="K61" s="74"/>
       <c r="L61" s="74"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
       <c r="D62" s="74"/>
@@ -26728,7 +26834,7 @@
       <c r="K62" s="74"/>
       <c r="L62" s="74"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
       <c r="D63" s="74"/>
@@ -26741,7 +26847,7 @@
       <c r="K63" s="74"/>
       <c r="L63" s="74"/>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
       <c r="D64" s="74"/>
@@ -26754,7 +26860,7 @@
       <c r="K64" s="74"/>
       <c r="L64" s="74"/>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
       <c r="D66" s="74"/>
@@ -26767,7 +26873,7 @@
       <c r="K66" s="74"/>
       <c r="L66" s="74"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="74"/>
       <c r="C67" s="74"/>
       <c r="D67" s="74"/>
@@ -26780,7 +26886,7 @@
       <c r="K67" s="74"/>
       <c r="L67" s="74"/>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="74"/>
       <c r="C68" s="74"/>
       <c r="D68" s="74"/>
@@ -26801,15 +26907,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7217B4B-89B8-4AC6-982A-7000E3238168}">
   <dimension ref="A1:L69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="3" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" hidden="1"/>
+    <col min="1" max="1" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="75"/>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -26823,7 +26929,7 @@
       <c r="K1" s="76"/>
       <c r="L1" s="76"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="75"/>
       <c r="B2" s="77"/>
       <c r="C2" s="77"/>
@@ -26837,7 +26943,7 @@
       <c r="K2" s="77"/>
       <c r="L2" s="77"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="74"/>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -26850,7 +26956,7 @@
       <c r="K4" s="74"/>
       <c r="L4" s="74"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="74"/>
       <c r="C5" s="74"/>
       <c r="D5" s="74"/>
@@ -26863,7 +26969,7 @@
       <c r="K5" s="74"/>
       <c r="L5" s="74"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="74"/>
       <c r="C6" s="74"/>
       <c r="D6" s="74"/>
@@ -26876,7 +26982,7 @@
       <c r="K6" s="74"/>
       <c r="L6" s="74"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -26889,7 +26995,7 @@
       <c r="K7" s="74"/>
       <c r="L7" s="74"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="74"/>
       <c r="C8" s="74"/>
       <c r="D8" s="74"/>
@@ -26902,7 +27008,7 @@
       <c r="K8" s="74"/>
       <c r="L8" s="74"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="74"/>
       <c r="C9" s="74"/>
       <c r="D9" s="74"/>
@@ -26915,7 +27021,7 @@
       <c r="K9" s="74"/>
       <c r="L9" s="74"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="74"/>
       <c r="C10" s="74"/>
       <c r="D10" s="74"/>
@@ -26928,7 +27034,7 @@
       <c r="K10" s="74"/>
       <c r="L10" s="74"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="74"/>
       <c r="C11" s="74"/>
       <c r="D11" s="74"/>
@@ -26941,7 +27047,7 @@
       <c r="K11" s="74"/>
       <c r="L11" s="74"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" s="74"/>
       <c r="C12" s="74"/>
       <c r="D12" s="74"/>
@@ -26954,7 +27060,7 @@
       <c r="K12" s="74"/>
       <c r="L12" s="74"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
       <c r="D13" s="74"/>
@@ -26967,7 +27073,7 @@
       <c r="K13" s="74"/>
       <c r="L13" s="74"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -26980,7 +27086,7 @@
       <c r="K14" s="74"/>
       <c r="L14" s="74"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="74"/>
       <c r="C15" s="74"/>
       <c r="D15" s="74"/>
@@ -26993,7 +27099,7 @@
       <c r="K15" s="74"/>
       <c r="L15" s="74"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="74"/>
       <c r="C16" s="74"/>
       <c r="D16" s="74"/>
@@ -27006,7 +27112,7 @@
       <c r="K16" s="74"/>
       <c r="L16" s="74"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="74"/>
       <c r="C17" s="74"/>
       <c r="D17" s="74"/>
@@ -27019,7 +27125,7 @@
       <c r="K17" s="74"/>
       <c r="L17" s="74"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="74"/>
       <c r="C18" s="74"/>
       <c r="D18" s="74"/>
@@ -27032,7 +27138,7 @@
       <c r="K18" s="74"/>
       <c r="L18" s="74"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
       <c r="D19" s="74"/>
@@ -27045,7 +27151,7 @@
       <c r="K19" s="74"/>
       <c r="L19" s="74"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
@@ -27058,7 +27164,7 @@
       <c r="K20" s="74"/>
       <c r="L20" s="74"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
       <c r="D21" s="74"/>
@@ -27071,7 +27177,7 @@
       <c r="K21" s="74"/>
       <c r="L21" s="74"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -27084,7 +27190,7 @@
       <c r="K22" s="74"/>
       <c r="L22" s="74"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -27097,7 +27203,7 @@
       <c r="K23" s="74"/>
       <c r="L23" s="74"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
@@ -27110,7 +27216,7 @@
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
@@ -27123,7 +27229,7 @@
       <c r="K25" s="74"/>
       <c r="L25" s="74"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
@@ -27136,7 +27242,7 @@
       <c r="K26" s="74"/>
       <c r="L26" s="74"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
       <c r="D27" s="74"/>
@@ -27149,7 +27255,7 @@
       <c r="K27" s="74"/>
       <c r="L27" s="74"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="74"/>
       <c r="C28" s="74"/>
       <c r="D28" s="74"/>
@@ -27162,7 +27268,7 @@
       <c r="K28" s="74"/>
       <c r="L28" s="74"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
       <c r="D29" s="74"/>
@@ -27175,7 +27281,7 @@
       <c r="K29" s="74"/>
       <c r="L29" s="74"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
       <c r="D30" s="74"/>
@@ -27188,7 +27294,7 @@
       <c r="K30" s="74"/>
       <c r="L30" s="74"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -27201,7 +27307,7 @@
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
@@ -27214,7 +27320,7 @@
       <c r="K32" s="74"/>
       <c r="L32" s="74"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
@@ -27227,7 +27333,7 @@
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>
@@ -27240,7 +27346,7 @@
       <c r="K34" s="74"/>
       <c r="L34" s="74"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>
@@ -27253,7 +27359,7 @@
       <c r="K35" s="74"/>
       <c r="L35" s="74"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="74"/>
       <c r="C36" s="74"/>
       <c r="D36" s="74"/>
@@ -27266,7 +27372,7 @@
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
@@ -27279,7 +27385,7 @@
       <c r="K37" s="74"/>
       <c r="L37" s="74"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
       <c r="D38" s="74"/>
@@ -27292,7 +27398,7 @@
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
       <c r="D39" s="74"/>
@@ -27305,7 +27411,7 @@
       <c r="K39" s="74"/>
       <c r="L39" s="74"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
       <c r="D40" s="74"/>
@@ -27318,7 +27424,7 @@
       <c r="K40" s="74"/>
       <c r="L40" s="74"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
       <c r="D41" s="74"/>
@@ -27331,7 +27437,7 @@
       <c r="K41" s="74"/>
       <c r="L41" s="74"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
       <c r="D42" s="74"/>
@@ -27344,7 +27450,7 @@
       <c r="K42" s="74"/>
       <c r="L42" s="74"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
       <c r="D43" s="74"/>
@@ -27357,7 +27463,7 @@
       <c r="K43" s="74"/>
       <c r="L43" s="74"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
       <c r="D44" s="74"/>
@@ -27370,7 +27476,7 @@
       <c r="K44" s="74"/>
       <c r="L44" s="74"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
       <c r="D45" s="74"/>
@@ -27383,7 +27489,7 @@
       <c r="K45" s="74"/>
       <c r="L45" s="74"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
@@ -27396,7 +27502,7 @@
       <c r="K46" s="74"/>
       <c r="L46" s="74"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="74"/>
       <c r="C47" s="74"/>
       <c r="D47" s="74"/>
@@ -27409,7 +27515,7 @@
       <c r="K47" s="74"/>
       <c r="L47" s="74"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="74"/>
       <c r="C48" s="74"/>
       <c r="D48" s="74"/>
@@ -27422,7 +27528,7 @@
       <c r="K48" s="74"/>
       <c r="L48" s="74"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="74"/>
       <c r="C49" s="74"/>
       <c r="D49" s="74"/>
@@ -27435,7 +27541,7 @@
       <c r="K49" s="74"/>
       <c r="L49" s="74"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50" s="74"/>
       <c r="C50" s="74"/>
       <c r="D50" s="74"/>
@@ -27448,7 +27554,7 @@
       <c r="K50" s="74"/>
       <c r="L50" s="74"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" s="74"/>
       <c r="C51" s="74"/>
       <c r="D51" s="74"/>
@@ -27461,7 +27567,7 @@
       <c r="K51" s="74"/>
       <c r="L51" s="74"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" s="74"/>
       <c r="C52" s="74"/>
       <c r="D52" s="74"/>
@@ -27474,7 +27580,7 @@
       <c r="K52" s="74"/>
       <c r="L52" s="74"/>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53" s="74"/>
       <c r="C53" s="74"/>
       <c r="D53" s="74"/>
@@ -27487,7 +27593,7 @@
       <c r="K53" s="74"/>
       <c r="L53" s="74"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54" s="74"/>
       <c r="C54" s="74"/>
       <c r="D54" s="74"/>
@@ -27500,7 +27606,7 @@
       <c r="K54" s="74"/>
       <c r="L54" s="74"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55" s="74"/>
       <c r="C55" s="74"/>
       <c r="D55" s="74"/>
@@ -27513,7 +27619,7 @@
       <c r="K55" s="74"/>
       <c r="L55" s="74"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" s="74"/>
       <c r="C56" s="74"/>
       <c r="D56" s="74"/>
@@ -27526,7 +27632,7 @@
       <c r="K56" s="74"/>
       <c r="L56" s="74"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57" s="74"/>
       <c r="C57" s="74"/>
       <c r="D57" s="74"/>
@@ -27539,7 +27645,7 @@
       <c r="K57" s="74"/>
       <c r="L57" s="74"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="74"/>
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
@@ -27552,7 +27658,7 @@
       <c r="K58" s="74"/>
       <c r="L58" s="74"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="74"/>
       <c r="C59" s="74"/>
       <c r="D59" s="74"/>
@@ -27565,7 +27671,7 @@
       <c r="K59" s="74"/>
       <c r="L59" s="74"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
       <c r="D60" s="74"/>
@@ -27578,7 +27684,7 @@
       <c r="K60" s="74"/>
       <c r="L60" s="74"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
       <c r="D61" s="74"/>
@@ -27591,7 +27697,7 @@
       <c r="K61" s="74"/>
       <c r="L61" s="74"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
       <c r="D62" s="74"/>
@@ -27604,7 +27710,7 @@
       <c r="K62" s="74"/>
       <c r="L62" s="74"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
       <c r="D63" s="74"/>
@@ -27617,7 +27723,7 @@
       <c r="K63" s="74"/>
       <c r="L63" s="74"/>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
       <c r="D64" s="74"/>
@@ -27630,7 +27736,7 @@
       <c r="K64" s="74"/>
       <c r="L64" s="74"/>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
       <c r="D65" s="74"/>
@@ -27643,19 +27749,19 @@
       <c r="K65" s="74"/>
       <c r="L65" s="74"/>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J66" s="74"/>
       <c r="K66" s="74"/>
       <c r="L66" s="74"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="74"/>
       <c r="H67" s="74"/>
       <c r="I67" s="74"/>
       <c r="J67" s="74"/>
       <c r="K67" s="74"/>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="74"/>
       <c r="C68" s="74"/>
       <c r="D68" s="74"/>
@@ -27667,7 +27773,7 @@
       <c r="J68" s="74"/>
       <c r="K68" s="74"/>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69" s="74"/>
       <c r="C69" s="74"/>
       <c r="D69" s="74"/>
